--- a/artfynd/S 4927-2021 artfynd.xlsx
+++ b/artfynd/S 4927-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96536173</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127495898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92226003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81008476</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126525266</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579485</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579381</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80708398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,8 +1711,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131787045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 4927-2021 artfynd.xlsx
+++ b/artfynd/S 4927-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,37 +907,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92226003</v>
+        <v>135593686</v>
       </c>
       <c r="B4" t="n">
-        <v>104628</v>
+        <v>107650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,17 +954,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övraböke, O vägen, Hl</t>
+          <t>Övraböke, 1240 m NO, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372377</v>
+        <v>373423</v>
       </c>
       <c r="R4" t="n">
-        <v>6310048</v>
+        <v>6311153</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,14 +986,19 @@
           <t>Slättåkra</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>N-Hal-2067</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,16 +1011,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Buskar</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägkant, stenmur</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1027,19 +1022,23 @@
           <t>Arne Lysell</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92226003</t>
+          <t>https://artportalen.se/Sighting/135593686</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81008476</v>
+        <v>92226003</v>
       </c>
       <c r="B5" t="n">
-        <v>97394</v>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,42 +1046,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Digeshult, V om, vid Möllesjön i SV, Hl</t>
+          <t>Övraböke, O vägen, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>374449</v>
+        <v>372377</v>
       </c>
       <c r="R5" t="n">
-        <v>6308162</v>
+        <v>6310048</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,12 +1116,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-11-20</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-11-20</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,43 +1130,44 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Buskar</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grandominerad blandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Lågor</t>
+          <t>Vägkant, stenmur</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kjell Georgson, Jesper Lind</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81008476</t>
+          <t>https://artportalen.se/Sighting/92226003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126525266</v>
+        <v>81008476</v>
       </c>
       <c r="B6" t="n">
-        <v>98194</v>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,45 +1175,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220686</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Möllesjöbäcken, Hl</t>
+          <t>Digeshult, V om, vid Möllesjön i SV, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>374516</v>
+        <v>374449</v>
       </c>
       <c r="R6" t="n">
-        <v>6307791</v>
+        <v>6308162</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,12 +1234,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2019-11-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2019-11-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,31 +1248,40 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grandominerad blandskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Lågor</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Kjell Georgson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Kjell Georgson, Jesper Lind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126525266</t>
+          <t>https://artportalen.se/Sighting/81008476</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111579485</v>
+        <v>126525266</v>
       </c>
       <c r="B7" t="n">
         <v>98194</v>
@@ -1303,17 +1320,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hasselbråten mot O2, Hl</t>
+          <t>Möllesjöbäcken, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>373468</v>
+        <v>374516</v>
       </c>
       <c r="R7" t="n">
-        <v>6298285</v>
+        <v>6307791</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,17 +1349,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Enslöv</t>
+          <t>Slättåkra</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,11 +1372,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Granåker kärr</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1374,13 +1386,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111579485</t>
+          <t>https://artportalen.se/Sighting/126525266</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111579381</v>
+        <v>111579485</v>
       </c>
       <c r="B8" t="n">
         <v>98194</v>
@@ -1419,14 +1431,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lövhult mot V2, Hl</t>
+          <t>Hasselbråten mot O2, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>374455</v>
+        <v>373468</v>
       </c>
       <c r="R8" t="n">
-        <v>6297150</v>
+        <v>6298285</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1473,7 +1485,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granåker skogsvägdike</t>
+          <t>Granåker kärr</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1490,13 +1502,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111579381</t>
+          <t>https://artportalen.se/Sighting/111579485</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80708398</v>
+        <v>111579381</v>
       </c>
       <c r="B9" t="n">
         <v>98194</v>
@@ -1535,17 +1547,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövhult mot VSV, Hl</t>
+          <t>Lövhult mot V2, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>374618</v>
+        <v>374455</v>
       </c>
       <c r="R9" t="n">
-        <v>6297003</v>
+        <v>6297150</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,12 +1581,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,7 +1601,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Skogskärr</t>
+          <t>Granåker skogsvägdike</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1606,16 +1618,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80708398</t>
+          <t>https://artportalen.se/Sighting/111579381</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131787045</v>
+        <v>80708398</v>
       </c>
       <c r="B10" t="n">
-        <v>96306</v>
+        <v>98194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,41 +1635,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2779</v>
+        <v>220686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pramma eke, Hl</t>
+          <t>Lövhult mot VSV, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373569</v>
+        <v>374618</v>
       </c>
       <c r="R10" t="n">
-        <v>6288915</v>
+        <v>6297003</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,17 +1692,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Övraby</t>
+          <t>Enslöv</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,19 +1715,131 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogskärr</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Lindström</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Lindström</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80708398</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131787045</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96306</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pramma eke, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>373569</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6288915</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Övraby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Lindström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Lindström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131787045</t>
         </is>
@@ -1728,6 +1856,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4927-2021 artfynd.xlsx
+++ b/artfynd/S 4927-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>135593686</v>
       </c>
       <c r="B4" t="n">
-        <v>107650</v>
+        <v>107705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 4927-2021 artfynd.xlsx
+++ b/artfynd/S 4927-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>135593686</v>
       </c>
       <c r="B4" t="n">
-        <v>107705</v>
+        <v>107732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
